--- a/samples/tracking01/tracking03.xlsx
+++ b/samples/tracking01/tracking03.xlsx
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>frame_index</t>
+          <t>frame_index_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
